--- a/companies/samsung-em/model.xlsx
+++ b/companies/samsung-em/model.xlsx
@@ -8244,7 +8244,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>905ed1de8424c7c0</t>
+          <t>160d3a76e03562a5</t>
         </is>
       </c>
     </row>

--- a/companies/samsung-em/model.xlsx
+++ b/companies/samsung-em/model.xlsx
@@ -8244,7 +8244,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>160d3a76e03562a5</t>
+          <t>2fbcdfae8a680785</t>
         </is>
       </c>
     </row>
